--- a/Excel/专业/专业主表导入.xlsx
+++ b/Excel/专业/专业主表导入.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="专业主表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="注意事项" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="专业主表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="注意事项" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +30,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +49,12 @@
         <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -63,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -71,6 +76,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,9 +443,278 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>专业代码</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>专业名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>学科名称</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>专业类型</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>学科门类</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>专业类</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>专业标签</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>授予学位</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>学制</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>就业率</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>薪资下限</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>薪资上限</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>专业描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>计算机科学与技术</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>计算机科学</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>工学</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>计算机类</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>热门,新工科</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>工学学士</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>四年</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>92.50</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>本专业培养具有良好科学素养，系统掌握计算机科学与技术的基本理论、方法和技能的高级专门人才</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>数学与应用数学</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>理学</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>数学类</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>基础学科</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>理学学士</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>四年</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>85.00</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>本专业培养掌握数学科学的基本理论与基本方法，具备运用数学知识、使用计算机解决实际问题能力的高级专门人才</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>080202</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>机械工程</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>机械工程</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>工学</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>机械类</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>传统工科</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>工学学士</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>四年</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>88.00</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>13000</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>本专业培养具备机械设计、制造及其自动化基础知识与应用能力的高级工程技术人才</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -449,291 +725,994 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>专业代码</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>专业名称</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>学科名称</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>专业类型</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>学科门类</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>专业类</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>专业标签</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>授予学位</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>学制</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>就业率</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>薪资下限</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>薪资上限</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>专业描述</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>一、导入说明</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>080901</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>计算机科学与技术</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>计算机科学</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>本科</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>工学</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>计算机类</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>热门,新工科</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>工学学士</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>四年</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>本专业培养具有良好科学素养，系统掌握计算机科学与技术的基本理论、方法和技能的高级专门人才</t>
+          <t>1. 文件格式：仅支持 .xlsx 格式</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>070101</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>数学与应用数学</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>本科</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>理学</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>数学类</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>基础学科</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>理学学士</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>四年</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>85.00</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>12000</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>本专业培养掌握数学科学的基本理论与基本方法，具备运用数学知识、使用计算机解决实际问题能力的高级专门人才</t>
+          <t>2. 行数限制：建议不超过 5000 行</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>080202</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>机械工程</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>机械工程</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>本科</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>工学</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>机械类</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>传统工科</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>工学学士</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>四年</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>88.00</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>5500</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>13000</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>本专业培养具备机械设计、制造及其自动化基础知识与应用能力的高级工程技术人才</t>
+          <t>3. 表头行：第 1 行（不可修改表头名称）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4. 数据起始行：第 2 行</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5. 编码：UTF-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>二、字段说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>校验规则</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>专业代码</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>唯一，不能与数据库已有值重复</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>入库字段：major_code</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>专业名称</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>不能为空</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>入库字段：major_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>学科名称</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>最大100字符</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>入库字段：discipline_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>专业类型</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>不能为空</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>入库字段：major_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>学科门类</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>最大50字符</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>入库字段：major_category</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>专业类</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>最大50字符</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>入库字段：parent_category</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>专业标签</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>逗号分隔多个标签</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>入库字段：major_tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>授予学位</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>最大50字符</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>入库字段：degree_awarded</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>学制</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>最大20字符</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>入库字段：study_duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>就业率</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NUMERIC(5,2)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0-100之间，如92.50</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>入库字段：employment_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>薪资下限</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>&gt;=0，单位：元/月</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>入库字段：salary_min</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>薪资上限</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>&gt;=0，且&gt;=薪资下限</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>入库字段：salary_max</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>专业描述</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>无长度限制</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>入库字段：description</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>三、数据库精度说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>精度</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>最多20字符</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>专业代码、学制等</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>最多30字符</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>专业类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>最多50字符</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>学科门类、专业类、专业标签、授予学位</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>最多100字符</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>专业名称、学科名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUMERIC(5,2)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>最多5位数字，2位小数</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>就业率（如：92.50）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>整数</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>薪资下限、薪资上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>无长度限制</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>专业描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>四、入库映射表</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Excel表头</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>DTO字段</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>数据库字段</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>数据库类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>专业代码</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>majorCode</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>major_code</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VARCHAR(20) NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>专业名称</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>majorName</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>major_name</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VARCHAR(100) NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>学科名称</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>disciplineName</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>discipline_name</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>专业类型</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>majorType</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>major_type</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VARCHAR(30) NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>学科门类</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>majorCategory</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>major_category</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>专业类</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>parentCategory</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>parent_category</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>专业标签</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>majorTags</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>major_tags</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>授予学位</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>degreeAwarded</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>degree_awarded</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>学制</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>studyDuration</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>study_duration</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>就业率</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>employmentRate</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>employment_rate</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NUMERIC(5,2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>薪资下限</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>salaryMin</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>salary_min</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>薪资上限</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>salaryMax</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>salary_max</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>专业描述</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>五、唯一性约束</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>约束名</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>uk_major_code</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>major_code</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>专业代码唯一，重复导入会报错</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>六、CHECK约束</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>约束名</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>chk_major_employment_rate</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>employment_rate</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>IS NULL OR (&gt;=0 AND &lt;=100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>chk_major_salary_range</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>salary_min, salary_max</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>salary_min &gt;=0 AND salary_max &gt;=0 AND salary_min &lt;= salary_max</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>